--- a/data/trans_orig/KIDM_C_3_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_3_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37917</t>
+          <t>37405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43052</t>
+          <t>43046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49087</t>
+          <t>48643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54032</t>
+          <t>54040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88343</t>
+          <t>89113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96383</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50235</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>28882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60765</t>
+          <t>60590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44836</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52520</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93806</t>
+          <t>93375</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101708</t>
+          <t>101158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68927</t>
+          <t>68645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60818</t>
+          <t>60691</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67963</t>
+          <t>67818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>123362</t>
+          <t>123019</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134459</t>
+          <t>134813</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>267627</t>
+          <t>267539</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>279758</t>
+          <t>280023</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>290262</t>
+          <t>290893</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>301527</t>
+          <t>301950</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>562125</t>
+          <t>562427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>579142</t>
+          <t>578627</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44629</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51767</t>
+          <t>51729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>50716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>82511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92864</t>
+          <t>93739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>22529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52243</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31686</t>
+          <t>31684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37124</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>64363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71286</t>
+          <t>71043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33043</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>454</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28509</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51900</t>
+          <t>51907</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>40550</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47351</t>
+          <t>47303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90153</t>
+          <t>90401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99360</t>
+          <t>99144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>37424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55977</t>
+          <t>55464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>60744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>51580</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64207</t>
+          <t>64091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102079</t>
+          <t>102592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120001</t>
+          <t>120632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>253780</t>
+          <t>253124</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>274935</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>275626</t>
+          <t>274975</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>295152</t>
+          <t>295013</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>535547</t>
+          <t>535924</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>563964</t>
+          <t>563372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43875</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>50771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48165</t>
+          <t>47852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50371</t>
+          <t>50148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55755</t>
+          <t>55750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101191</t>
+          <t>101087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107381</t>
+          <t>107392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29242</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64549</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31306</t>
+          <t>31363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>34823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>55832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>65532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>39799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25688</t>
+          <t>25009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55453</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60765</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58439</t>
+          <t>57976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66686</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54614</t>
+          <t>55838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62913</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118174</t>
+          <t>117792</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128405</t>
+          <t>128431</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39606</t>
+          <t>39474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>59238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70235</t>
+          <t>70401</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54755</t>
+          <t>54209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66024</t>
+          <t>65811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117287</t>
+          <t>117419</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133245</t>
+          <t>133621</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>304730</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>323217</t>
+          <t>322406</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>304614</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>323032</t>
+          <t>322663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>614919</t>
+          <t>615268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>640305</t>
+          <t>640333</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54653</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>53514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109969</t>
+          <t>111264</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118895</t>
+          <t>118977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,42 +11428,42 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>4005</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4005</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21413</t>
+          <t>21100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44560</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>32056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34843</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40500</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66409</t>
+          <t>66748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>72178</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60237</t>
+          <t>59808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75899</t>
+          <t>76826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139230</t>
+          <t>138037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>196989</t>
+          <t>196202</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>206875</t>
+          <t>206603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>260482</t>
+          <t>260348</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>268824</t>
+          <t>268826</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>459965</t>
+          <t>460629</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>472950</t>
+          <t>474059</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
